--- a/data/trans_orig/P04C04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>517497</t>
+          <t>518342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>564518</t>
+          <t>562642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>450897</t>
+          <t>451039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>623324</t>
+          <t>623309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>977314</t>
+          <t>944209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1175628</t>
+          <t>1173633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66640</t>
+          <t>68808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113997</t>
+          <t>112566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98889</t>
+          <t>98616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>271062</t>
+          <t>271522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177298</t>
+          <t>179279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>378092</t>
+          <t>409508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449843</t>
+          <t>374609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1049934</t>
+          <t>1042666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802940</t>
+          <t>800660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>836404</t>
+          <t>835994</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1126526</t>
+          <t>1069324</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1863466</t>
+          <t>1866375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36665</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115704</t>
+          <t>119825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>729866</t>
+          <t>802654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104289</t>
+          <t>105171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136974</t>
+          <t>139974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242628</t>
+          <t>241366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>992548</t>
+          <t>1056733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>542501</t>
+          <t>538920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>592842</t>
+          <t>591686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>791242</t>
+          <t>790440</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>887903</t>
+          <t>876918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1350542</t>
+          <t>1350017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1490019</t>
+          <t>1485784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108078</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158757</t>
+          <t>160729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133391</t>
+          <t>135129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141498</t>
+          <t>141340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277243</t>
+          <t>275735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>753128</t>
+          <t>752615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>801442</t>
+          <t>802369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>717986</t>
+          <t>695400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>929527</t>
+          <t>930712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1458920</t>
+          <t>1443581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1711822</t>
+          <t>1711419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46367</t>
+          <t>47836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109148</t>
+          <t>106945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155396</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>142980</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>358907</t>
+          <t>380312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>270922</t>
+          <t>271799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>530542</t>
+          <t>534095</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2102193</t>
+          <t>2147876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2942420</t>
+          <t>2941233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2889787</t>
+          <t>2872427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3208364</t>
+          <t>3200684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5102985</t>
+          <t>5088981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6071938</t>
+          <t>6071245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>60444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,47 +2717,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>79903</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>61555</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>101236</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>79903</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>60537</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>100332</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>463856</t>
+          <t>466962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1317017</t>
+          <t>1275292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>461788</t>
+          <t>461635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>784780</t>
+          <t>791573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>998771</t>
+          <t>1000538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1989538</t>
+          <t>2000420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Habitat-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>545962</t>
+          <t>595335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>518342</t>
+          <t>571487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>562642</t>
+          <t>613239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>86,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>82,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>628065</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>612186</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>641185</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>83,64%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1223400</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1195134</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1247560</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>86,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>577492</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>451039</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>623309</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>62,37%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1123453</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>944209</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1173633</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -838,44 +838,44 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9979</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>869</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8837</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84891</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68808</t>
+          <t>72916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112566</t>
+          <t>114528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144750</t>
+          <t>102957</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98616</t>
+          <t>90178</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>271522</t>
+          <t>118507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>229641</t>
+          <t>193668</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>179279</t>
+          <t>170168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>409508</t>
+          <t>221327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>723142</t>
+          <t>731890</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>723142</t>
+          <t>731890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>723142</t>
+          <t>731890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1357564</t>
+          <t>1421514</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1357564</t>
+          <t>1421514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1357564</t>
+          <t>1421514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>822203</t>
+          <t>907786</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374609</t>
+          <t>880902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1042666</t>
+          <t>932004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>820131</t>
+          <t>913348</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>800660</t>
+          <t>895085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>835994</t>
+          <t>932424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1642334</t>
+          <t>1821135</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1069324</t>
+          <t>1786180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1866375</t>
+          <t>1850182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>42945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>61381</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>346953</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119825</t>
+          <t>91754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>802654</t>
+          <t>137291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>120824</t>
+          <t>136881</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105171</t>
+          <t>118475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139974</t>
+          <t>156159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>467777</t>
+          <t>248739</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241366</t>
+          <t>221160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1056733</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192336</t>
+          <t>1048367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192336</t>
+          <t>1048367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192336</t>
+          <t>1048367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>955711</t>
+          <t>1067502</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>955711</t>
+          <t>1067502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>955711</t>
+          <t>1067502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2115869</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2115869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2115869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570038</t>
+          <t>651910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538920</t>
+          <t>624182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>591686</t>
+          <t>675473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>827681</t>
+          <t>684999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>790440</t>
+          <t>661363</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>876918</t>
+          <t>703431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1397719</t>
+          <t>1336909</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1350017</t>
+          <t>1305490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1485784</t>
+          <t>1370224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130654</t>
+          <t>145817</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109107</t>
+          <t>122316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160729</t>
+          <t>174376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>99153</t>
+          <t>119731</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>101835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135129</t>
+          <t>144026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>229807</t>
+          <t>265548</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141340</t>
+          <t>232914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>275735</t>
+          <t>297950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>799514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>799514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>799514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>931537</t>
+          <t>810262</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931537</t>
+          <t>810262</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>931537</t>
+          <t>810262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1633773</t>
+          <t>1609776</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1633773</t>
+          <t>1609776</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1633773</t>
+          <t>1609776</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>779230</t>
+          <t>837018</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>752615</t>
+          <t>810024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>802369</t>
+          <t>859604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>863872</t>
+          <t>943115</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>695400</t>
+          <t>920505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>930712</t>
+          <t>962212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1643102</t>
+          <t>1780133</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1443581</t>
+          <t>1744434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1711419</t>
+          <t>1811757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47836</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106945</t>
+          <t>113044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156459</t>
+          <t>160112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>210800</t>
+          <t>154365</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142980</t>
+          <t>136447</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>380312</t>
+          <t>175423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>340833</t>
+          <t>288518</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271799</t>
+          <t>256871</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>534095</t>
+          <t>321749</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>923275</t>
+          <t>985017</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>923275</t>
+          <t>985017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>923275</t>
+          <t>985017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1091909</t>
+          <t>1115898</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1091909</t>
+          <t>1115898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1091909</t>
+          <t>1115898</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2015184</t>
+          <t>2100915</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2015184</t>
+          <t>2100915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2015184</t>
+          <t>2100915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2717431</t>
+          <t>2992049</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2147876</t>
+          <t>2941745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2941233</t>
+          <t>3041609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3089176</t>
+          <t>3169527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2872427</t>
+          <t>3128514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3200684</t>
+          <t>3202815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5806606</t>
+          <t>6161577</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5088981</t>
+          <t>6098313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6071245</t>
+          <t>6219832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>67060</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61555</t>
+          <t>72820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101236</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>692530</t>
+          <t>482539</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>466962</t>
+          <t>436883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1275292</t>
+          <t>532983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>575527</t>
+          <t>513934</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>461635</t>
+          <t>480572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>791573</t>
+          <t>552839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>996473</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1000538</t>
+          <t>936725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2000420</t>
+          <t>1062275</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
